--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_oil_gas_production_and_exploration.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-3.75366568914956</v>
+        <v>-2.471180046111926</v>
       </c>
       <c r="H2">
-        <v>-3.75366568914956</v>
+        <v>-2.471180046111926</v>
       </c>
       <c r="I2">
-        <v>-5.010166596674039</v>
+        <v>-4.197240169698707</v>
       </c>
       <c r="J2">
-        <v>-5.010166596674039</v>
+        <v>-4.197240169698707</v>
       </c>
       <c r="K2">
-        <v>-27.46</v>
+        <v>-23.42</v>
       </c>
       <c r="L2">
-        <v>-7.320714476139695</v>
+        <v>-4.908824145881367</v>
       </c>
       <c r="M2">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.001880504641751964</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.002876911871813547</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.079</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>10.436</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="V2">
-        <v>0.2484170435610569</v>
+        <v>0.1916666666666667</v>
       </c>
       <c r="W2">
-        <v>-0.15234375</v>
+        <v>-0.1789473684210527</v>
       </c>
       <c r="X2">
-        <v>0.07089070879412432</v>
+        <v>0.1224021697862421</v>
       </c>
       <c r="Y2">
-        <v>-0.2232344587941243</v>
+        <v>-0.3013495382072948</v>
       </c>
       <c r="Z2">
-        <v>0.04704057324726035</v>
+        <v>0.03680612501185413</v>
       </c>
       <c r="AA2">
-        <v>-0.1618204804045512</v>
+        <v>-0.153738644304682</v>
       </c>
       <c r="AB2">
-        <v>0.07078941761685734</v>
+        <v>0.1213714906825938</v>
       </c>
       <c r="AC2">
-        <v>-0.2325171366241073</v>
+        <v>-0.2751101349872758</v>
       </c>
       <c r="AD2">
-        <v>1.266</v>
+        <v>1.841</v>
       </c>
       <c r="AE2">
-        <v>0.05567452062160635</v>
+        <v>0.005164248162654867</v>
       </c>
       <c r="AF2">
-        <v>1.321674520621606</v>
+        <v>1.846164248162655</v>
       </c>
       <c r="AG2">
-        <v>-9.114325479378394</v>
+        <v>-8.043835751837346</v>
       </c>
       <c r="AH2">
-        <v>0.0305013488456953</v>
+        <v>0.03454250223814932</v>
       </c>
       <c r="AI2">
-        <v>0.009151496996615199</v>
+        <v>0.0126305855918078</v>
       </c>
       <c r="AJ2">
-        <v>-0.2770675966429816</v>
+        <v>-0.1846773215843188</v>
       </c>
       <c r="AK2">
-        <v>-0.06802462660271652</v>
+        <v>-0.05902599178818461</v>
       </c>
       <c r="AL2">
-        <v>6.02</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AM2">
-        <v>5.85</v>
+        <v>-6.478</v>
       </c>
       <c r="AN2">
-        <v>-0.08547123953551175</v>
+        <v>-0.1549141703130259</v>
       </c>
       <c r="AO2">
-        <v>-3.129568106312293</v>
+        <v>-238.452380952381</v>
       </c>
       <c r="AP2">
-        <v>0.6153338832958678</v>
+        <v>0.6768626516187601</v>
       </c>
       <c r="AQ2">
-        <v>-3.220512820512821</v>
+        <v>3.092003704847175</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Petro Matad Limited (DB:HA3)</t>
+          <t>TomCo Energy Plc (AIM:TOM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,31 +713,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-101.6129032258064</v>
+        <v>-68.33333333333333</v>
       </c>
       <c r="H3">
-        <v>-101.6129032258064</v>
+        <v>-68.33333333333333</v>
       </c>
       <c r="I3">
-        <v>-60.42370658465552</v>
+        <v>-61.66666666666667</v>
       </c>
       <c r="J3">
-        <v>-60.42370658465552</v>
+        <v>-61.66666666666667</v>
       </c>
       <c r="K3">
-        <v>-1.91</v>
+        <v>-13.1</v>
       </c>
       <c r="L3">
-        <v>-61.61290322580645</v>
+        <v>-436.6666666666667</v>
       </c>
       <c r="M3">
-        <v>0.079</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.003376068376068376</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.04136125654450262</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,76 +749,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.079</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.376</v>
+        <v>1.48</v>
       </c>
       <c r="V3">
-        <v>0.01606837606837607</v>
+        <v>0.2027397260273973</v>
       </c>
       <c r="W3">
-        <v>-0.107909604519774</v>
+        <v>-0.7401129943502825</v>
       </c>
       <c r="X3">
-        <v>0.07089070879412432</v>
+        <v>0.1382778633661617</v>
       </c>
       <c r="Y3">
-        <v>-0.1788003133138983</v>
+        <v>-0.8783908577164443</v>
       </c>
       <c r="Z3">
-        <v>0.001976325593091007</v>
+        <v>0.002054794520547945</v>
       </c>
       <c r="AA3">
-        <v>-0.1194169177526763</v>
+        <v>-0.1267123287671233</v>
       </c>
       <c r="AB3">
-        <v>0.07078941761685734</v>
+        <v>0.1253747738727721</v>
       </c>
       <c r="AC3">
-        <v>-0.1902063353695337</v>
+        <v>-0.2520871026398954</v>
       </c>
       <c r="AD3">
-        <v>0.026</v>
+        <v>1.59</v>
       </c>
       <c r="AE3">
-        <v>0.05567452062160635</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.08167452062160635</v>
+        <v>1.59</v>
       </c>
       <c r="AG3">
-        <v>-0.2943254793783937</v>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.003478223861329812</v>
+        <v>0.1788526434195725</v>
       </c>
       <c r="AI3">
-        <v>0.005344605429947615</v>
+        <v>0.1890606420927467</v>
       </c>
       <c r="AJ3">
-        <v>-0.0127382335934712</v>
+        <v>0.01484480431848854</v>
       </c>
       <c r="AK3">
-        <v>-0.01974586785530585</v>
+        <v>0.01587301587301589</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AM3">
-        <v>-0.011</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AN3">
-        <v>-0.01527614571092832</v>
+        <v>-0.8641304347826086</v>
+      </c>
+      <c r="AO3">
+        <v>-22.02380952380952</v>
       </c>
       <c r="AP3">
-        <v>0.1729291888239681</v>
+        <v>-0.05978260869565222</v>
       </c>
       <c r="AQ3">
-        <v>174.5454545454546</v>
+        <v>-22.02380952380952</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TomCo Energy Plc (AIM:TOM)</t>
+          <t>Challenger Energy Group PLC (AIM:CEG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,8 +837,23 @@
           <t>Oil/Gas (Production and Exploration)</t>
         </is>
       </c>
+      <c r="G4">
+        <v>-1.613924050632911</v>
+      </c>
+      <c r="H4">
+        <v>-1.613924050632911</v>
+      </c>
+      <c r="I4">
+        <v>-3.248945147679325</v>
+      </c>
+      <c r="J4">
+        <v>-3.248945147679325</v>
+      </c>
       <c r="K4">
-        <v>-1.95</v>
+        <v>-7.6</v>
+      </c>
+      <c r="L4">
+        <v>-1.60337552742616</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -865,67 +877,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3.1</v>
+        <v>5.31</v>
       </c>
       <c r="V4">
-        <v>0.2672413793103449</v>
+        <v>0.4962616822429907</v>
       </c>
       <c r="W4">
-        <v>-0.15234375</v>
+        <v>-0.06877828054298642</v>
       </c>
       <c r="X4">
-        <v>0.07069665621955609</v>
+        <v>0.1224021697862421</v>
       </c>
       <c r="Y4">
-        <v>-0.2230404062195561</v>
+        <v>-0.1911804503292285</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>0.04731955675351902</v>
       </c>
       <c r="AA4">
-        <v>-0.1618204804045512</v>
+        <v>-0.153738644304682</v>
       </c>
       <c r="AB4">
-        <v>0.07069665621955609</v>
+        <v>0.1213714906825938</v>
       </c>
       <c r="AC4">
-        <v>-0.2325171366241073</v>
+        <v>-0.2751101349872758</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.251</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.251</v>
       </c>
       <c r="AG4">
-        <v>-3.1</v>
+        <v>-5.058999999999999</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.02292028125285362</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.002168447788788002</v>
       </c>
       <c r="AJ4">
-        <v>-0.3647058823529412</v>
+        <v>-0.8968268037581988</v>
       </c>
       <c r="AK4">
-        <v>-0.2167832167832168</v>
+        <v>-0.04580726360681268</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-6.51</v>
       </c>
       <c r="AN4">
-        <v>-0</v>
+        <v>-0.03433652530779754</v>
       </c>
       <c r="AP4">
-        <v>1.62303664921466</v>
+        <v>0.6920656634746921</v>
+      </c>
+      <c r="AQ4">
+        <v>2.365591397849462</v>
       </c>
     </row>
     <row r="5">
@@ -936,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Challenger Energy Group PLC (AIM:CEG)</t>
+          <t>Petro Matad Limited (DB:HA3)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -945,22 +960,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>-2.580645161290323</v>
+        <v>-2090</v>
       </c>
       <c r="H5">
-        <v>-2.580645161290323</v>
+        <v>-2090</v>
       </c>
       <c r="I5">
-        <v>-4.032258064516129</v>
+        <v>-2775.032849632531</v>
       </c>
       <c r="J5">
-        <v>-4.032258064516129</v>
+        <v>-2775.032849632531</v>
       </c>
       <c r="K5">
-        <v>-23.6</v>
+        <v>-2.72</v>
       </c>
       <c r="L5">
-        <v>-6.344086021505376</v>
+        <v>-2720</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -984,73 +999,70 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>6.96</v>
+        <v>3.1</v>
       </c>
       <c r="V5">
-        <v>0.9928673323823111</v>
+        <v>0.09226190476190477</v>
       </c>
       <c r="W5">
-        <v>-0.367601246105919</v>
+        <v>-0.1789473684210527</v>
       </c>
       <c r="X5">
-        <v>0.0805311574623877</v>
+        <v>0.1204985395025707</v>
       </c>
       <c r="Y5">
-        <v>-0.4481324035683067</v>
+        <v>-0.2994459079236234</v>
       </c>
       <c r="Z5">
-        <v>0.07127938837686103</v>
+        <v>6.731665724420946e-05</v>
       </c>
       <c r="AA5">
-        <v>-0.2874168886163751</v>
+        <v>-0.1868059351801349</v>
       </c>
       <c r="AB5">
-        <v>0.07470511561302082</v>
+        <v>0.1205048917249417</v>
       </c>
       <c r="AC5">
-        <v>-0.3621220042293959</v>
+        <v>-0.3073108269050766</v>
       </c>
       <c r="AD5">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.005164248162654867</v>
       </c>
       <c r="AF5">
-        <v>1.24</v>
+        <v>0.005164248162654867</v>
       </c>
       <c r="AG5">
-        <v>-5.72</v>
+        <v>-3.094835751837345</v>
       </c>
       <c r="AH5">
-        <v>0.1503030303030303</v>
+        <v>0.0001536742425812491</v>
       </c>
       <c r="AI5">
-        <v>0.01109718990513693</v>
+        <v>0.0002346834635913277</v>
       </c>
       <c r="AJ5">
-        <v>-4.434108527131783</v>
+        <v>-0.1014528466937774</v>
       </c>
       <c r="AK5">
-        <v>-0.05459057071960297</v>
+        <v>-0.1637031930118314</v>
       </c>
       <c r="AL5">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.861</v>
+        <v>-0.052</v>
       </c>
       <c r="AN5">
-        <v>-0.1107142857142857</v>
-      </c>
-      <c r="AO5">
-        <v>-2.491694352159469</v>
+        <v>-0</v>
       </c>
       <c r="AP5">
-        <v>0.5107142857142857</v>
+        <v>1.131980889479643</v>
       </c>
       <c r="AQ5">
-        <v>-2.559290223511346</v>
+        <v>53.46153846153846</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_oil_gas_production_and_exploration.xlsx
@@ -587,23 +587,26 @@
           <t>Oil/Gas (Production and Exploration)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.61</v>
+      </c>
       <c r="G2">
-        <v>-2.471180046111926</v>
+        <v>-3.028131634819533</v>
       </c>
       <c r="H2">
-        <v>-2.471180046111926</v>
+        <v>-3.028131634819533</v>
       </c>
       <c r="I2">
-        <v>-4.197240169698707</v>
+        <v>-3.710191082802548</v>
       </c>
       <c r="J2">
-        <v>-4.197240169698707</v>
+        <v>-3.710191082802548</v>
       </c>
       <c r="K2">
-        <v>-23.42</v>
+        <v>-7.18</v>
       </c>
       <c r="L2">
-        <v>-4.908824145881367</v>
+        <v>-1.90552016985138</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9.890000000000001</v>
+        <v>2.628</v>
       </c>
       <c r="V2">
-        <v>0.1916666666666667</v>
+        <v>0.04730021598272138</v>
       </c>
       <c r="W2">
-        <v>-0.1789473684210527</v>
+        <v>-0.1468181818181818</v>
       </c>
       <c r="X2">
-        <v>0.1224021697862421</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="Y2">
-        <v>-0.3013495382072948</v>
+        <v>-0.2382936245700925</v>
       </c>
       <c r="Z2">
-        <v>0.03680612501185413</v>
+        <v>0.02861895322077153</v>
       </c>
       <c r="AA2">
-        <v>-0.153738644304682</v>
+        <v>-0.180952380952381</v>
       </c>
       <c r="AB2">
-        <v>0.1213714906825938</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="AC2">
-        <v>-0.2751101349872758</v>
+        <v>-0.2724278237042917</v>
       </c>
       <c r="AD2">
-        <v>1.841</v>
+        <v>0.751</v>
       </c>
       <c r="AE2">
-        <v>0.005164248162654867</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.846164248162655</v>
+        <v>0.751</v>
       </c>
       <c r="AG2">
-        <v>-8.043835751837346</v>
+        <v>-1.877</v>
       </c>
       <c r="AH2">
-        <v>0.03454250223814932</v>
+        <v>0.0133366482570013</v>
       </c>
       <c r="AI2">
-        <v>0.0126305855918078</v>
+        <v>0.005319412668843541</v>
       </c>
       <c r="AJ2">
-        <v>-0.1846773215843188</v>
+        <v>-0.03496451390570571</v>
       </c>
       <c r="AK2">
-        <v>-0.05902599178818461</v>
+        <v>-0.01354716245768767</v>
       </c>
       <c r="AL2">
-        <v>0.08400000000000001</v>
+        <v>2.483</v>
       </c>
       <c r="AM2">
-        <v>-6.478</v>
+        <v>2.003</v>
       </c>
       <c r="AN2">
-        <v>-0.1549141703130259</v>
+        <v>-0.0864211737629459</v>
       </c>
       <c r="AO2">
-        <v>-238.452380952381</v>
+        <v>-5.63028594442207</v>
       </c>
       <c r="AP2">
-        <v>0.6768626516187601</v>
+        <v>0.2159953970080552</v>
       </c>
       <c r="AQ2">
-        <v>3.092003704847175</v>
+        <v>-6.979530703944084</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TomCo Energy Plc (AIM:TOM)</t>
+          <t>Challenger Energy Group PLC (AIM:CEG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,22 +716,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-68.33333333333333</v>
+        <v>-1.927953890489914</v>
       </c>
       <c r="H3">
-        <v>-68.33333333333333</v>
+        <v>-1.927953890489914</v>
       </c>
       <c r="I3">
-        <v>-61.66666666666667</v>
+        <v>-2.619596541786744</v>
       </c>
       <c r="J3">
-        <v>-61.66666666666667</v>
+        <v>-2.619596541786744</v>
       </c>
       <c r="K3">
-        <v>-13.1</v>
+        <v>-2.15</v>
       </c>
       <c r="L3">
-        <v>-436.6666666666667</v>
+        <v>-0.6195965417867435</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +755,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="V3">
-        <v>0.2027397260273973</v>
+        <v>0.1341463414634146</v>
       </c>
       <c r="W3">
-        <v>-0.7401129943502825</v>
+        <v>-0.01861471861471862</v>
       </c>
       <c r="X3">
-        <v>0.1382778633661617</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="Y3">
-        <v>-0.8783908577164443</v>
+        <v>-0.1100901613666293</v>
       </c>
       <c r="Z3">
-        <v>0.002054794520547945</v>
+        <v>0.03278812446258658</v>
       </c>
       <c r="AA3">
-        <v>-0.1267123287671233</v>
+        <v>-0.08589165745386512</v>
       </c>
       <c r="AB3">
-        <v>0.1253747738727721</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="AC3">
-        <v>-0.2520871026398954</v>
+        <v>-0.1773671002057758</v>
       </c>
       <c r="AD3">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.1100000000000001</v>
+        <v>-1.65</v>
       </c>
       <c r="AH3">
-        <v>0.1788526434195725</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.1890606420927467</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.01484480431848854</v>
+        <v>-0.1549295774647887</v>
       </c>
       <c r="AK3">
-        <v>0.01587301587301589</v>
+        <v>-0.01545667447306791</v>
       </c>
       <c r="AL3">
-        <v>0.08400000000000001</v>
+        <v>1.93</v>
       </c>
       <c r="AM3">
-        <v>0.08400000000000001</v>
+        <v>1.642</v>
       </c>
       <c r="AN3">
-        <v>-0.8641304347826086</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-22.02380952380952</v>
+        <v>-4.709844559585492</v>
       </c>
       <c r="AP3">
-        <v>-0.05978260869565222</v>
+        <v>0.3101503759398496</v>
       </c>
       <c r="AQ3">
-        <v>-22.02380952380952</v>
+        <v>-5.535931790499391</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Challenger Energy Group PLC (AIM:CEG)</t>
+          <t>Petro Matad Limited (DB:HA3)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,23 +840,26 @@
           <t>Oil/Gas (Production and Exploration)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.61</v>
+      </c>
       <c r="G4">
-        <v>-1.613924050632911</v>
+        <v>-24</v>
       </c>
       <c r="H4">
-        <v>-1.613924050632911</v>
+        <v>-24</v>
       </c>
       <c r="I4">
-        <v>-3.248945147679325</v>
+        <v>-26.30769230769231</v>
       </c>
       <c r="J4">
-        <v>-3.248945147679325</v>
+        <v>-26.30769230769231</v>
       </c>
       <c r="K4">
-        <v>-7.6</v>
+        <v>-3.23</v>
       </c>
       <c r="L4">
-        <v>-1.60337552742616</v>
+        <v>-24.84615384615385</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,70 +883,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.31</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="V4">
-        <v>0.4962616822429907</v>
+        <v>0.02068527918781726</v>
       </c>
       <c r="W4">
-        <v>-0.06877828054298642</v>
+        <v>-0.1468181818181818</v>
       </c>
       <c r="X4">
-        <v>0.1224021697862421</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="Y4">
-        <v>-0.1911804503292285</v>
+        <v>-0.2382936245700925</v>
       </c>
       <c r="Z4">
-        <v>0.04731955675351902</v>
+        <v>0.006878306878306879</v>
       </c>
       <c r="AA4">
-        <v>-0.153738644304682</v>
+        <v>-0.180952380952381</v>
       </c>
       <c r="AB4">
-        <v>0.1213714906825938</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="AC4">
-        <v>-0.2751101349872758</v>
+        <v>-0.2724278237042917</v>
       </c>
       <c r="AD4">
-        <v>0.251</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.251</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-5.058999999999999</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.02292028125285362</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.002168447788788002</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.8968268037581988</v>
+        <v>-0.02112219774523778</v>
       </c>
       <c r="AK4">
-        <v>-0.04580726360681268</v>
+        <v>-0.03383848868590409</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-6.51</v>
+        <v>-0.192</v>
       </c>
       <c r="AN4">
-        <v>-0.03433652530779754</v>
+        <v>-0</v>
       </c>
       <c r="AP4">
-        <v>0.6920656634746921</v>
+        <v>0.2418397626112759</v>
       </c>
       <c r="AQ4">
-        <v>2.365591397849462</v>
+        <v>17.8125</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Petro Matad Limited (DB:HA3)</t>
+          <t>TomCo Energy Plc (AIM:TOM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,22 +966,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>-2090</v>
+        <v>-9.523809523809524</v>
       </c>
       <c r="H5">
-        <v>-2090</v>
+        <v>-9.523809523809524</v>
       </c>
       <c r="I5">
-        <v>-2775.032849632531</v>
+        <v>-8.75</v>
       </c>
       <c r="J5">
-        <v>-2775.032849632531</v>
+        <v>-8.75</v>
       </c>
       <c r="K5">
-        <v>-2.72</v>
+        <v>-1.8</v>
       </c>
       <c r="L5">
-        <v>-2720</v>
+        <v>-10.71428571428571</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -999,70 +1005,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>3.1</v>
+        <v>0.163</v>
       </c>
       <c r="V5">
-        <v>0.09226190476190477</v>
+        <v>0.0422279792746114</v>
       </c>
       <c r="W5">
-        <v>-0.1789473684210527</v>
+        <v>-0.2639296187683284</v>
       </c>
       <c r="X5">
-        <v>0.1204985395025707</v>
+        <v>0.101723955059342</v>
       </c>
       <c r="Y5">
-        <v>-0.2994459079236234</v>
+        <v>-0.3656535738276705</v>
       </c>
       <c r="Z5">
-        <v>6.731665724420946e-05</v>
+        <v>0.02424242424242425</v>
       </c>
       <c r="AA5">
-        <v>-0.1868059351801349</v>
+        <v>-0.2121212121212121</v>
       </c>
       <c r="AB5">
-        <v>0.1205048917249417</v>
+        <v>0.09613507580871387</v>
       </c>
       <c r="AC5">
-        <v>-0.3073108269050766</v>
+        <v>-0.308256287929926</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.751</v>
       </c>
       <c r="AE5">
-        <v>0.005164248162654867</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.005164248162654867</v>
+        <v>0.751</v>
       </c>
       <c r="AG5">
-        <v>-3.094835751837345</v>
+        <v>0.588</v>
       </c>
       <c r="AH5">
-        <v>0.0001536742425812491</v>
+        <v>0.1628713944914335</v>
       </c>
       <c r="AI5">
-        <v>0.0002346834635913277</v>
+        <v>0.09529247557416572</v>
       </c>
       <c r="AJ5">
-        <v>-0.1014528466937774</v>
+        <v>0.1321942446043166</v>
       </c>
       <c r="AK5">
-        <v>-0.1637031930118314</v>
+        <v>0.07618554029541331</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.553</v>
       </c>
       <c r="AM5">
-        <v>-0.052</v>
-      </c>
-      <c r="AN5">
-        <v>-0</v>
-      </c>
-      <c r="AP5">
-        <v>1.131980889479643</v>
+        <v>0.553</v>
+      </c>
+      <c r="AO5">
+        <v>-2.658227848101265</v>
       </c>
       <c r="AQ5">
-        <v>53.46153846153846</v>
+        <v>-2.658227848101265</v>
       </c>
     </row>
   </sheetData>
